--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04587568167306</v>
+        <v>1.632454798271873</v>
       </c>
       <c r="D2" t="n">
-        <v>10.52453457389075</v>
+        <v>1.710236868257247</v>
       </c>
       <c r="E2" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F2" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.09636453452756</v>
+        <v>7.653159236860729</v>
       </c>
       <c r="D3" t="n">
-        <v>46.43359729285435</v>
+        <v>7.545459560088832</v>
       </c>
       <c r="E3" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F3" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.54983551341637</v>
+        <v>4.15184827093016</v>
       </c>
       <c r="D4" t="n">
-        <v>25.81854353153559</v>
+        <v>4.195513323874533</v>
       </c>
       <c r="E4" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F4" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.21204379249532</v>
+        <v>4.25945711628049</v>
       </c>
       <c r="D5" t="n">
-        <v>26.2530020331965</v>
+        <v>4.266112830394431</v>
       </c>
       <c r="E5" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F5" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.86929300027246</v>
+        <v>5.503760112544276</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45729422979375</v>
+        <v>5.599310312341485</v>
       </c>
       <c r="E6" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F6" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.6013808594243</v>
+        <v>3.02272438965645</v>
       </c>
       <c r="D7" t="n">
-        <v>19.10669240507939</v>
+        <v>3.104837515825401</v>
       </c>
       <c r="E7" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F7" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.46855022824296</v>
+        <v>2.676139412089482</v>
       </c>
       <c r="D8" t="n">
-        <v>16.45581014808202</v>
+        <v>2.674069149063328</v>
       </c>
       <c r="E8" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F8" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.25485069091068</v>
+        <v>1.666413237272985</v>
       </c>
       <c r="D9" t="n">
-        <v>10.70325924863671</v>
+        <v>1.739279627903465</v>
       </c>
       <c r="E9" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F9" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.80410078741335</v>
+        <v>7.28066637795467</v>
       </c>
       <c r="D10" t="n">
-        <v>44.82868717644848</v>
+        <v>7.284661666172878</v>
       </c>
       <c r="E10" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F10" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.42385234215047</v>
+        <v>2.343876005599451</v>
       </c>
       <c r="D11" t="n">
-        <v>13.89745629783225</v>
+        <v>2.25833664839774</v>
       </c>
       <c r="E11" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F11" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.2349716659079</v>
+        <v>4.588182895710035</v>
       </c>
       <c r="D12" t="n">
-        <v>28.60095875422116</v>
+        <v>4.647655797560938</v>
       </c>
       <c r="E12" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F12" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.66263532114534</v>
+        <v>6.445178239686118</v>
       </c>
       <c r="D13" t="n">
-        <v>39.13314329914546</v>
+        <v>6.359135786111137</v>
       </c>
       <c r="E13" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F13" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.97659089285498</v>
+        <v>6.658696020088934</v>
       </c>
       <c r="D14" t="n">
-        <v>40.3878136117911</v>
+        <v>6.563019711916055</v>
       </c>
       <c r="E14" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F14" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>60.86784926330304</v>
+        <v>9.891025505286745</v>
       </c>
       <c r="D15" t="n">
-        <v>60.29136497619341</v>
+        <v>9.797346808631429</v>
       </c>
       <c r="E15" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F15" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.77326984083883</v>
+        <v>4.51315634913631</v>
       </c>
       <c r="D16" t="n">
-        <v>27.46267856382337</v>
+        <v>4.462685266621297</v>
       </c>
       <c r="E16" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F16" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99615066782335</v>
+        <v>5.524374483521295</v>
       </c>
       <c r="D17" t="n">
-        <v>33.93756526953281</v>
+        <v>5.514854356299082</v>
       </c>
       <c r="E17" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F17" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.74922491457401</v>
+        <v>6.296749048618277</v>
       </c>
       <c r="D18" t="n">
-        <v>38.17406595751731</v>
+        <v>6.203285718096564</v>
       </c>
       <c r="E18" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F18" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>39.19183028838382</v>
+        <v>6.368672421862371</v>
       </c>
       <c r="D19" t="n">
-        <v>38.77938386277243</v>
+        <v>6.301649877700521</v>
       </c>
       <c r="E19" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F19" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>48.27767584916403</v>
+        <v>7.845122325489155</v>
       </c>
       <c r="D20" t="n">
-        <v>48.08566688998437</v>
+        <v>7.81392086962246</v>
       </c>
       <c r="E20" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F20" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>60.99360891755614</v>
+        <v>9.911461449102873</v>
       </c>
       <c r="D21" t="n">
-        <v>60.90435395645972</v>
+        <v>9.896957517924704</v>
       </c>
       <c r="E21" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F21" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>51.67255660168439</v>
+        <v>8.396790447773714</v>
       </c>
       <c r="D22" t="n">
-        <v>51.23905568098151</v>
+        <v>8.326346548159496</v>
       </c>
       <c r="E22" t="n">
-        <v>14.88679317824432</v>
+        <v>2.419103891464702</v>
       </c>
       <c r="F22" t="n">
-        <v>14.66523193663135</v>
+        <v>2.383100189702595</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
